--- a/learning.xlsx
+++ b/learning.xlsx
@@ -8,12 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hemlata\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{292778E1-BFB0-474B-B6C1-2A867555459E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C42369-1E95-48B4-8089-4862D74F703B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{169ABADE-9E16-416D-9770-513F2194103D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="6" xr2:uid="{169ABADE-9E16-416D-9770-513F2194103D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="115">
   <si>
     <t>ID</t>
   </si>
@@ -166,13 +172,229 @@
   </si>
   <si>
     <t>Net Amount</t>
+  </si>
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Join Date</t>
+  </si>
+  <si>
+    <t>Leave Balance</t>
+  </si>
+  <si>
+    <t>Basic Salary</t>
+  </si>
+  <si>
+    <t>Bonus%</t>
+  </si>
+  <si>
+    <t>Project Start</t>
+  </si>
+  <si>
+    <t>Project End</t>
+  </si>
+  <si>
+    <t>Weekday Joined</t>
+  </si>
+  <si>
+    <t>John Doe</t>
+  </si>
+  <si>
+    <t>john@example.com</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Jane Smith</t>
+  </si>
+  <si>
+    <t>jane@example.com</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Alice Johnson</t>
+  </si>
+  <si>
+    <t>alice@example.com</t>
+  </si>
+  <si>
+    <t>Bob brown</t>
+  </si>
+  <si>
+    <t>bob@example</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>eva@example.com</t>
+  </si>
+  <si>
+    <t>Eva White</t>
+  </si>
+  <si>
+    <t>BOB brown</t>
+  </si>
+  <si>
+    <t>John       Doe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Jane Smith</t>
+  </si>
+  <si>
+    <t>Alice    Johnson</t>
+  </si>
+  <si>
+    <t>Full Name-Trim</t>
+  </si>
+  <si>
+    <t>Full Name - Proper</t>
+  </si>
+  <si>
+    <t>Email - Lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abc </t>
+  </si>
+  <si>
+    <t>BOB@example.com</t>
+  </si>
+  <si>
+    <t>Domain - Right</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bob</t>
+  </si>
+  <si>
+    <t>john</t>
+  </si>
+  <si>
+    <t>example.com</t>
+  </si>
+  <si>
+    <t>jane</t>
+  </si>
+  <si>
+    <t>alice</t>
+  </si>
+  <si>
+    <t>BOB</t>
+  </si>
+  <si>
+    <t>eva</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>Jane</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Alic</t>
+  </si>
+  <si>
+    <t>e Johnson</t>
+  </si>
+  <si>
+    <t>brown</t>
+  </si>
+  <si>
+    <t>Eva</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>doe</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sales</t>
+  </si>
+  <si>
+    <t>today</t>
+  </si>
+  <si>
+    <t>yesterday</t>
+  </si>
+  <si>
+    <t>tommorrow</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Hour</t>
+  </si>
+  <si>
+    <t>Second</t>
+  </si>
+  <si>
+    <t>Minute</t>
+  </si>
+  <si>
+    <t>datediff</t>
+  </si>
+  <si>
+    <t>Networking days</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,6 +432,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -234,10 +464,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -250,8 +481,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -267,8 +504,2185 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.18191513560804901"/>
+          <c:y val="0.13004629629629633"/>
+          <c:w val="0.7634181977252843"/>
+          <c:h val="0.46567767570720325"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet6!$A$2:$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>John Doe</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10-05-2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet6!$D$1:$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Basic Salary</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Month</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Day</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Project Start</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Project End</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet6!$D$2:$I$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>50000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="m/d/yyyy">
+                  <c:v>45444</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="m/d/yyyy">
+                  <c:v>45444</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3474-49DE-A203-9E3AB2D8C001}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet6!$A$3:$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Jane Smith</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15-01-2023</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet6!$D$1:$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Basic Salary</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Month</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Day</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Project Start</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Project End</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet6!$D$3:$I$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>60000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="m/d/yyyy">
+                  <c:v>45444</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="m/d/yyyy">
+                  <c:v>45461</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3474-49DE-A203-9E3AB2D8C001}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet6!$A$4:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Alice Johnson</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>01-07-2021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet6!$D$1:$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Basic Salary</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Month</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Day</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Project Start</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Project End</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet6!$D$4:$I$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>55000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="m/d/yyyy">
+                  <c:v>45444</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="m/d/yyyy">
+                  <c:v>45463</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3474-49DE-A203-9E3AB2D8C001}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet6!$A$5:$C$5</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Bob brown</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20-10-2023</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>HR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet6!$D$1:$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Basic Salary</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Month</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Day</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Project Start</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Project End</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet6!$D$5:$I$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="m/d/yyyy">
+                  <c:v>45444</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="m/d/yyyy">
+                  <c:v>45468</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3474-49DE-A203-9E3AB2D8C001}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet6!$A$6:$C$6</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Eva White</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>05-03-2020</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet6!$D$1:$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Basic Salary</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Month</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Day</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Project Start</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Project End</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet6!$D$6:$I$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>70000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="m/d/yyyy">
+                  <c:v>45444</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="m/d/yyyy">
+                  <c:v>45473</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-3474-49DE-A203-9E3AB2D8C001}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="2128867200"/>
+        <c:axId val="1961712048"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2128867200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1961712048"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1961712048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2128867200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet7!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Join Date</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet7!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>John Doe</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Jane Smith</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alice Johnson</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Bob brown</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Eva White</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet7!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>44691</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44941</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44378</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45219</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43895</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F5A7-4AD0-9E20-909AE5EA37F1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="2130268512"/>
+        <c:axId val="1961705808"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2130268512"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1961705808"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1961705808"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2130268512"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>568325</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>263525</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A03E3340-F076-930F-A6B2-077CD2C7BC02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>22225</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>327025</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00C2304D-2E4F-2361-0A48-CFB3F55558BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1037,4 +3451,1523 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBAF607C-B648-4763-B06B-7058CCB299F7}">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.08984375" customWidth="1"/>
+    <col min="4" max="4" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="4">
+        <v>44691</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>50000</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2" s="4">
+        <v>45444</v>
+      </c>
+      <c r="K2" s="4">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4">
+        <v>44941</v>
+      </c>
+      <c r="G3">
+        <v>12</v>
+      </c>
+      <c r="H3">
+        <v>60000</v>
+      </c>
+      <c r="I3">
+        <v>0.15</v>
+      </c>
+      <c r="J3" s="4">
+        <v>45444</v>
+      </c>
+      <c r="K3" s="4">
+        <v>45461</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="4">
+        <v>44378</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>55000</v>
+      </c>
+      <c r="I4">
+        <v>0.1</v>
+      </c>
+      <c r="J4" s="4">
+        <v>45444</v>
+      </c>
+      <c r="K4" s="4">
+        <v>45463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="4">
+        <v>45219</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>45000</v>
+      </c>
+      <c r="I5">
+        <v>0.05</v>
+      </c>
+      <c r="J5" s="4">
+        <v>45444</v>
+      </c>
+      <c r="K5" s="4">
+        <v>45468</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="4">
+        <v>43895</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>70000</v>
+      </c>
+      <c r="I6">
+        <v>0.2</v>
+      </c>
+      <c r="J6" s="4">
+        <v>45444</v>
+      </c>
+      <c r="K6" s="4">
+        <v>45473</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{4BD86EB1-29E6-4A8D-ACB2-ABA32592448B}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{7DD18E0D-B727-4BD3-8C05-33335C751DFC}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{94185AEE-7F61-40AF-B54A-AEED7471C3E6}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{2170E2C0-8738-4278-83E1-CC0EA1E31C05}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{46E7DC22-F729-49B5-BC74-C5D9795EFB52}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3FCA749-EE56-4835-B90C-DDCF8B828F3B}">
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.08984375" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E15" s="6"/>
+      <c r="H15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I15" t="str">
+        <f xml:space="preserve"> UPPER(H15)</f>
+        <v xml:space="preserve">ABC </v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="str">
+        <f>TRIM(A18)</f>
+        <v>John Doe</v>
+      </c>
+      <c r="D18" t="str">
+        <f xml:space="preserve"> PROPER(C18)</f>
+        <v>John Doe</v>
+      </c>
+      <c r="E18" t="str">
+        <f xml:space="preserve"> LOWER(B18)</f>
+        <v>john@example.com</v>
+      </c>
+      <c r="F18" t="str">
+        <f xml:space="preserve"> RIGHT(E18,11)</f>
+        <v>example.com</v>
+      </c>
+      <c r="G18" t="str">
+        <f xml:space="preserve"> LEFT(C18,3)</f>
+        <v>Joh</v>
+      </c>
+      <c r="H18" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" t="s">
+        <v>79</v>
+      </c>
+      <c r="J18" t="s">
+        <v>88</v>
+      </c>
+      <c r="K18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" ref="C19:C22" si="0">TRIM(A19)</f>
+        <v>Jane Smith</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" ref="D19:D22" si="1" xml:space="preserve"> PROPER(C19)</f>
+        <v>Jane Smith</v>
+      </c>
+      <c r="E19" t="str">
+        <f xml:space="preserve"> LOWER(B19)</f>
+        <v>jane@example.com</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" ref="F19:F22" si="2" xml:space="preserve"> RIGHT(E19,11)</f>
+        <v>example.com</v>
+      </c>
+      <c r="G19" t="str">
+        <f xml:space="preserve"> LEFT(C19,3)</f>
+        <v>Jan</v>
+      </c>
+      <c r="H19" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" t="s">
+        <v>79</v>
+      </c>
+      <c r="J19" t="s">
+        <v>90</v>
+      </c>
+      <c r="K19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>Alice Johnson</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="1"/>
+        <v>Alice Johnson</v>
+      </c>
+      <c r="E20" t="str">
+        <f xml:space="preserve"> LOWER(B20)</f>
+        <v>alice@example.com</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="2"/>
+        <v>example.com</v>
+      </c>
+      <c r="G20" t="str">
+        <f xml:space="preserve"> LEFT(C20,3)</f>
+        <v>Ali</v>
+      </c>
+      <c r="H20" t="s">
+        <v>81</v>
+      </c>
+      <c r="I20" t="s">
+        <v>79</v>
+      </c>
+      <c r="J20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>BOB brown</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="1"/>
+        <v>Bob Brown</v>
+      </c>
+      <c r="E21" t="str">
+        <f xml:space="preserve"> LOWER(B21)</f>
+        <v>bob@example.com</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="2"/>
+        <v>example.com</v>
+      </c>
+      <c r="G21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" t="s">
+        <v>82</v>
+      </c>
+      <c r="K21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>Eva White</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="1"/>
+        <v>Eva White</v>
+      </c>
+      <c r="E22" t="str">
+        <f xml:space="preserve"> LOWER(B22)</f>
+        <v>eva@example.com</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="2"/>
+        <v>example.com</v>
+      </c>
+      <c r="G22" t="str">
+        <f xml:space="preserve"> LEFT(C22,3)</f>
+        <v>Eva</v>
+      </c>
+      <c r="H22" t="s">
+        <v>83</v>
+      </c>
+      <c r="I22" t="s">
+        <v>79</v>
+      </c>
+      <c r="J22" t="s">
+        <v>95</v>
+      </c>
+      <c r="K22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" t="str">
+        <f xml:space="preserve"> D26&amp;E26</f>
+        <v>johndoe</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" t="str">
+        <f>D27&amp;" " &amp;E27</f>
+        <v>john doe</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(D28,E28)</f>
+        <v>johndoe</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(D29," ",E29)</f>
+        <v>john doe</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D30" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" t="s">
+        <v>97</v>
+      </c>
+      <c r="F30" t="str">
+        <f xml:space="preserve"> _xlfn.TEXTJOIN("-",FALSE,D30,E30)</f>
+        <v>john-doe</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D31" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" t="str">
+        <f>_xlfn.TEXTJOIN("-",TRUE,D31,E31)</f>
+        <v>john</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D32" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" t="str">
+        <f xml:space="preserve"> _xlfn.TEXTJOIN("-",FALSE,D32,E32)</f>
+        <v>john-</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{F80D624F-7B2E-4D95-9BA8-7B1926E17F85}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{8C4B3D32-2D28-4B89-B956-6386E2FD1542}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{A3EF1FFC-FACD-41EC-A2B4-AE1376D6EBE8}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{8DFF9659-8458-4ACD-92C1-C6A35C632591}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{BED3D396-2277-4C3F-8E40-21FE7E06FF67}"/>
+    <hyperlink ref="B8" r:id="rId6" xr:uid="{4CA89D0E-F87B-49CA-AF2B-FAE7AF0EFB12}"/>
+    <hyperlink ref="B7" r:id="rId7" xr:uid="{53AE91D9-85F9-4965-A21B-CFCFEA004277}"/>
+    <hyperlink ref="E10" r:id="rId8" xr:uid="{4439D805-312B-46BF-AB12-55A6850B9A6A}"/>
+    <hyperlink ref="E11" r:id="rId9" xr:uid="{A2183185-91BA-4AFF-A264-53463B82F355}"/>
+    <hyperlink ref="E12" r:id="rId10" xr:uid="{A16DE941-D521-45F1-A2A1-139F12F37B8A}"/>
+    <hyperlink ref="E13" r:id="rId11" xr:uid="{07AA8277-0AA9-4C0A-8BF5-76C45B69D2BA}"/>
+    <hyperlink ref="E14" r:id="rId12" xr:uid="{CF2B7E60-90A8-4E38-8517-3E30CBE49D8B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2B8678-038B-4523-9E32-8534128E0146}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11">
+        <v>55000</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate leftLabels="1" topLabels="1">
+    <dataRefs count="1">
+      <dataRef ref="A1:B6" sheet="Sheet4"/>
+    </dataRefs>
+  </dataConsolidate>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B374E79C-EF77-4403-870D-FE04E431313D}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="4">
+        <v>44691</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2">
+        <v>50000</v>
+      </c>
+      <c r="E2">
+        <f xml:space="preserve"> YEAR(B2)</f>
+        <v>2022</v>
+      </c>
+      <c r="F2">
+        <f xml:space="preserve"> MONTH(B2)</f>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <f xml:space="preserve"> DAY(B2)</f>
+        <v>10</v>
+      </c>
+      <c r="H2" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I2" s="4">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="4">
+        <v>44941</v>
+      </c>
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3">
+        <v>60000</v>
+      </c>
+      <c r="E3">
+        <f xml:space="preserve"> YEAR(B3)</f>
+        <v>2023</v>
+      </c>
+      <c r="F3">
+        <f xml:space="preserve"> MONTH(B3)</f>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <f xml:space="preserve"> DAY(B3)</f>
+        <v>15</v>
+      </c>
+      <c r="H3" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I3" s="4">
+        <v>45461</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="4">
+        <v>44378</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4">
+        <v>55000</v>
+      </c>
+      <c r="E4">
+        <f xml:space="preserve"> YEAR(B4)</f>
+        <v>2021</v>
+      </c>
+      <c r="F4">
+        <f xml:space="preserve"> MONTH(B4)</f>
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <f xml:space="preserve"> DAY(B4)</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I4" s="4">
+        <v>45463</v>
+      </c>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="4">
+        <v>45219</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5">
+        <v>45000</v>
+      </c>
+      <c r="E5">
+        <f xml:space="preserve"> YEAR(B5)</f>
+        <v>2023</v>
+      </c>
+      <c r="F5">
+        <f xml:space="preserve"> MONTH(B5)</f>
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <f xml:space="preserve"> DAY(B5)</f>
+        <v>20</v>
+      </c>
+      <c r="H5" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I5" s="4">
+        <v>45468</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="4">
+        <v>43895</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6">
+        <v>70000</v>
+      </c>
+      <c r="E6">
+        <f xml:space="preserve"> YEAR(B6)</f>
+        <v>2020</v>
+      </c>
+      <c r="F6">
+        <f xml:space="preserve"> MONTH(B6)</f>
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <f xml:space="preserve"> DAY(B6)</f>
+        <v>5</v>
+      </c>
+      <c r="H6" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I6" s="4">
+        <v>45473</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="4">
+        <f ca="1" xml:space="preserve"> TODAY()</f>
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="4">
+        <f ca="1">TODAY()-1</f>
+        <v>46271</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.51636574074074071</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="4">
+        <f ca="1" xml:space="preserve"> TODAY()+1</f>
+        <v>46273</v>
+      </c>
+      <c r="D13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13">
+        <f>HOUR(E12)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14">
+        <f xml:space="preserve"> MINUTE(E12)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15">
+        <f xml:space="preserve"> SECOND(E12)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17">
+        <f ca="1" xml:space="preserve"> DATEDIF(Sheet6!B2,TODAY(),"y")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18">
+        <f ca="1" xml:space="preserve"> NETWORKDAYS(Sheet6!B2,TODAY())</f>
+        <v>1130</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB6E8B3-D324-4813-8C70-3E5782BF4C5D}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="4">
+        <v>44691</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2">
+        <v>50000</v>
+      </c>
+      <c r="E2">
+        <f xml:space="preserve"> YEAR(B2)</f>
+        <v>2022</v>
+      </c>
+      <c r="F2">
+        <f xml:space="preserve"> MONTH(B2)</f>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <f xml:space="preserve"> DAY(B2)</f>
+        <v>10</v>
+      </c>
+      <c r="H2" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I2" s="4">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="4">
+        <v>44941</v>
+      </c>
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3">
+        <v>60000</v>
+      </c>
+      <c r="E3">
+        <f xml:space="preserve"> YEAR(B3)</f>
+        <v>2023</v>
+      </c>
+      <c r="F3">
+        <f xml:space="preserve"> MONTH(B3)</f>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <f xml:space="preserve"> DAY(B3)</f>
+        <v>15</v>
+      </c>
+      <c r="H3" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I3" s="4">
+        <v>45461</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="4">
+        <v>44378</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4">
+        <v>55000</v>
+      </c>
+      <c r="E4">
+        <f xml:space="preserve"> YEAR(B4)</f>
+        <v>2021</v>
+      </c>
+      <c r="F4">
+        <f xml:space="preserve"> MONTH(B4)</f>
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <f xml:space="preserve"> DAY(B4)</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I4" s="4">
+        <v>45463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="4">
+        <v>45219</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5">
+        <v>45000</v>
+      </c>
+      <c r="E5">
+        <f xml:space="preserve"> YEAR(B5)</f>
+        <v>2023</v>
+      </c>
+      <c r="F5">
+        <f xml:space="preserve"> MONTH(B5)</f>
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <f xml:space="preserve"> DAY(B5)</f>
+        <v>20</v>
+      </c>
+      <c r="H5" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I5" s="4">
+        <v>45468</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="4">
+        <v>43895</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6">
+        <v>70000</v>
+      </c>
+      <c r="E6">
+        <f xml:space="preserve"> YEAR(B6)</f>
+        <v>2020</v>
+      </c>
+      <c r="F6">
+        <f xml:space="preserve"> MONTH(B6)</f>
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <f xml:space="preserve"> DAY(B6)</f>
+        <v>5</v>
+      </c>
+      <c r="H6" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I6" s="4">
+        <v>45473</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6070C614-4CA4-47E0-A404-C5007F106CB8}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="4">
+        <v>44691</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2">
+        <v>50000</v>
+      </c>
+      <c r="E2">
+        <f xml:space="preserve"> YEAR(B2)</f>
+        <v>2022</v>
+      </c>
+      <c r="F2">
+        <f xml:space="preserve"> MONTH(B2)</f>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <f xml:space="preserve"> DAY(B2)</f>
+        <v>10</v>
+      </c>
+      <c r="H2" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I2" s="4">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="4">
+        <v>44941</v>
+      </c>
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3">
+        <v>60000</v>
+      </c>
+      <c r="E3">
+        <f xml:space="preserve"> YEAR(B3)</f>
+        <v>2023</v>
+      </c>
+      <c r="F3">
+        <f xml:space="preserve"> MONTH(B3)</f>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <f xml:space="preserve"> DAY(B3)</f>
+        <v>15</v>
+      </c>
+      <c r="H3" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I3" s="4">
+        <v>45461</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="4">
+        <v>44378</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4">
+        <v>55000</v>
+      </c>
+      <c r="E4">
+        <f xml:space="preserve"> YEAR(B4)</f>
+        <v>2021</v>
+      </c>
+      <c r="F4">
+        <f xml:space="preserve"> MONTH(B4)</f>
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <f xml:space="preserve"> DAY(B4)</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I4" s="4">
+        <v>45463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="4">
+        <v>45219</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5">
+        <v>45000</v>
+      </c>
+      <c r="E5">
+        <f xml:space="preserve"> YEAR(B5)</f>
+        <v>2023</v>
+      </c>
+      <c r="F5">
+        <f xml:space="preserve"> MONTH(B5)</f>
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <f xml:space="preserve"> DAY(B5)</f>
+        <v>20</v>
+      </c>
+      <c r="H5" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I5" s="4">
+        <v>45468</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="4">
+        <v>43895</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6">
+        <v>70000</v>
+      </c>
+      <c r="E6">
+        <f xml:space="preserve"> YEAR(B6)</f>
+        <v>2020</v>
+      </c>
+      <c r="F6">
+        <f xml:space="preserve"> MONTH(B6)</f>
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <f xml:space="preserve"> DAY(B6)</f>
+        <v>5</v>
+      </c>
+      <c r="H6" s="4">
+        <v>45444</v>
+      </c>
+      <c r="I6" s="4">
+        <v>45473</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>